--- a/reports/history/android/build-16/Excel/Failed_Test_Cases.xlsx
+++ b/reports/history/android/build-16/Excel/Failed_Test_Cases.xlsx
@@ -477,17 +477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="4628" customWidth="1" min="8" max="8"/>
+    <col width="9568" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -543,22 +543,22 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC_AUTH_010</t>
+          <t>TC_GEN_003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Password Field Toggle Visibility</t>
+          <t>test_home_page_load</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -568,323 +568,134 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 05:38:59</t>
+          <t>2026-06-23 16:31:25</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>shared_driver = &lt;test_regression_400.shared_driver.&lt;locals&gt;.MockDriver object at 0x7f958cd3b690&gt;
-tc = {'id': 'TC_AUTH_010', 'module': 'Authentication', 'name': 'Password Field Toggle Visibility', 'priority': 'Low', ...}
-    @pytest.mark.parametrize("tc", test_cases, ids=lambda x: x["id"])
-    def test_regression_case(shared_driver, tc):
-        """Executes the specific test case via hybrid or simulated path."""
-        test_id = tc["id"]
-        module = tc["module"]
-        name = tc["name"]
-        is_mock = not hasattr(shared_driver, "find_element")
-        print(f"\n[Running Test] {test_id} - {name} ({module})")
-        # 1. Active Appium Session (Live Hybrid Actions)
-        if not is_mock:
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;
+    @pytest.fixture(scope="function")
+    def auth_driver(driver):
+        """Fixture to launch app and log in automatically with test credentials."""
+        time.sleep(5)
+        login_page = LoginPage(driver)
+        print("[MobileTest] Performing E2E test login...")
+&gt;       login_page.login("testfarmer@example.com", "TestFarmer123!")
+tests/mobile_e2e/test_suites/test_features.py:14: 
+_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
+tests/mobile_e2e/pages/login_page.py:14: in login
+    self.send_keys(self.EMAIL_INPUT, email)
+tests/mobile_e2e/pages/base_page.py:31: in send_keys
+    element = self.wait_for_element(locator)
+              ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
+    raise e
+tests/mobile_e2e/pages/base_page.py:17: in wait_for_element
+    return WebDriverWait(self.driver, self.timeout).until(
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/wait.py:112: in until
+    value = method(self._driver)
+            ^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/expected_conditions.py:188: in _predicate
+    return _element_if_visible(driver.find_element(*locator))
+                               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:899: in find_element
+    return self.execute(Command.FIND_ELEMENT, {"using": by, "value": value})["value"]
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
+    self.error_handler.check_response(response)
+_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f052231b410&gt;
+response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10510ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
+    def check_response(self, response: Dict[str, Any]) -&gt; None:
+        """
+        https://www.w3.org/TR/webdriver/#errors
+        """
+        payload = response.get('value', '')
+        if isinstance(payload, dict):
+            payload_dict = payload
+        else:
             try:
-                # Login E2E
-                if test_id == "TC_AUTH_001":
-                    login_page = LoginPage(shared_driver)
-                    login_page.login("testfarmer@example.com", "TestFarmer123!")
-                    time.sleep(4)
-                    home_page = HomePage(shared_driver)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Login verification failed"
-                    home_page.capture_screenshot("TC_AUTH_001_success")
-                # Quick Actions grid scroll/check
-                elif test_id == "TC_DASH_002":
-                    home_page = HomePage(shared_driver)
-                    home_page.swipe(720, 1600, 720, 800, 300)
-                    assert home_page.wait_for_element(home_page.MARKET_TILE) is not None, "Quick Actions grid failed to scroll/load"
-                    home_page.capture_screenshot("TC_DASH_002_success")
-                # Navigate to Crops Screen
-                elif test_id == "TC_NAV_001":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.CROPS_TAB)
-                    crops_title = (By.XPATH, "//*[contains(@content-desc, 'Farm Management')] | //*[contains(@text, 'Farm Management')]")
-                    assert home_page.wait_for_element(crops_title) is not None, "Navigation to Crops failed"
-                    home_page.capture_screenshot("TC_NAV_001_success")
-                # Navigation back to Home
-                elif test_id == "TC_NAV_003":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.HOME_TAB)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Navigation back to Home failed"
-                    home_page.capture_screenshot("TC_NAV_003_success")
-                # Simulated actions for others when driver is active
-                else:
-                    # Basic assertion to pass successfully
-                    assert tc["status"] == "passed"
-            except Exception as e:
-                # Save screenshot on failure
-                screenshots_dir = os.path.join(
-                    os.path.dirname(os.path.dirname(os.path.abspath(__file__))),
-                    "Test Results", "Screenshots"
-                )
-                os.makedirs(screenshots_dir, exist_ok=True)
-                screenshot_path = os.path.join(screenshots_dir, f"fail_{test_id}.png")
-                try:
-                    shared_driver.save_screenshot(screenshot_path)
-                except Exception:
-                    pass
-                raise e
-        # 2. Simulated Execution (No live Appium driver - local unit testing or regression scale)
-        else:
-            # Verify correctness of test case data structure
-            assert tc["id"] is not None
-            assert tc["module"] is not None
-            assert tc["name"] is not None
-            assert tc["priority"] in ["Critical", "High", "Medium", "Low"]
-            assert len(tc["steps"]) &gt; 0
-            assert tc["expected"] is not None
-            # Simulate some test cases failing to test reporting and failure criteria if needed
-            # (For regression verification, we will ensure &gt;95% pass rate so the workflow passes)
-            if test_id in ["TC_AUTH_010", "TC_FORM_008", "TC_FILE_002"]:
-                # Intentionally fail these 3 test cases to match the failure examples in summary
-                tc["status"] = "failed"
-                tc["actual_result"] = "Validation elements missing or mismatch"
-&gt;               raise AssertionError(f"Simulated failure for {test_id}: {tc['actual_result']}")
-E               AssertionError: Simulated failure for TC_AUTH_010: Validation elements missing or mismatch
-tests/mobile_e2e/test_suites/test_regression_400.py:145: AssertionError</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>TC_FORM_008</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Multi-step Form Progress Indicator - Scenario Variant 1</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 05:38:59</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>shared_driver = &lt;test_regression_400.shared_driver.&lt;locals&gt;.MockDriver object at 0x7f958cd3b690&gt;
-tc = {'id': 'TC_FORM_008', 'module': 'Forms', 'name': 'Multi-step Form Progress Indicator - Scenario Variant 1', 'priority': 'Low', ...}
-    @pytest.mark.parametrize("tc", test_cases, ids=lambda x: x["id"])
-    def test_regression_case(shared_driver, tc):
-        """Executes the specific test case via hybrid or simulated path."""
-        test_id = tc["id"]
-        module = tc["module"]
-        name = tc["name"]
-        is_mock = not hasattr(shared_driver, "find_element")
-        print(f"\n[Running Test] {test_id} - {name} ({module})")
-        # 1. Active Appium Session (Live Hybrid Actions)
-        if not is_mock:
-            try:
-                # Login E2E
-                if test_id == "TC_AUTH_001":
-                    login_page = LoginPage(shared_driver)
-                    login_page.login("testfarmer@example.com", "TestFarmer123!")
-                    time.sleep(4)
-                    home_page = HomePage(shared_driver)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Login verification failed"
-                    home_page.capture_screenshot("TC_AUTH_001_success")
-                # Quick Actions grid scroll/check
-                elif test_id == "TC_DASH_002":
-                    home_page = HomePage(shared_driver)
-                    home_page.swipe(720, 1600, 720, 800, 300)
-                    assert home_page.wait_for_element(home_page.MARKET_TILE) is not None, "Quick Actions grid failed to scroll/load"
-                    home_page.capture_screenshot("TC_DASH_002_success")
-                # Navigate to Crops Screen
-                elif test_id == "TC_NAV_001":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.CROPS_TAB)
-                    crops_title = (By.XPATH, "//*[contains(@content-desc, 'Farm Management')] | //*[contains(@text, 'Farm Management')]")
-                    assert home_page.wait_for_element(crops_title) is not None, "Navigation to Crops failed"
-                    home_page.capture_screenshot("TC_NAV_001_success")
-                # Navigation back to Home
-                elif test_id == "TC_NAV_003":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.HOME_TAB)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Navigation back to Home failed"
-                    home_page.capture_screenshot("TC_NAV_003_success")
-                # Simulated actions for others when driver is active
-                else:
-                    # Basic assertion to pass successfully
-                    assert tc["status"] == "passed"
-            except Exception as e:
-                # Save screenshot on failure
-                screenshots_dir = os.path.join(
-                    os.path.dirname(os.path.dirname(os.path.abspath(__file__))),
-                    "Test Results", "Screenshots"
-                )
-                os.makedirs(screenshots_dir, exist_ok=True)
-                screenshot_path = os.path.join(screenshots_dir, f"fail_{test_id}.png")
-                try:
-                    shared_driver.save_screenshot(screenshot_path)
-                except Exception:
-                    pass
-                raise e
-        # 2. Simulated Execution (No live Appium driver - local unit testing or regression scale)
-        else:
-            # Verify correctness of test case data structure
-            assert tc["id"] is not None
-            assert tc["module"] is not None
-            assert tc["name"] is not None
-            assert tc["priority"] in ["Critical", "High", "Medium", "Low"]
-            assert len(tc["steps"]) &gt; 0
-            assert tc["expected"] is not None
-            # Simulate some test cases failing to test reporting and failure criteria if needed
-            # (For regression verification, we will ensure &gt;95% pass rate so the workflow passes)
-            if test_id in ["TC_AUTH_010", "TC_FORM_008", "TC_FILE_002"]:
-                # Intentionally fail these 3 test cases to match the failure examples in summary
-                tc["status"] = "failed"
-                tc["actual_result"] = "Validation elements missing or mismatch"
-&gt;               raise AssertionError(f"Simulated failure for {test_id}: {tc['actual_result']}")
-E               AssertionError: Simulated failure for TC_FORM_008: Validation elements missing or mismatch
-tests/mobile_e2e/test_suites/test_regression_400.py:145: AssertionError</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>TC_FILE_002</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Upload Leaf Image JPG Format</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 05:38:59</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>shared_driver = &lt;test_regression_400.shared_driver.&lt;locals&gt;.MockDriver object at 0x7f958cd3b690&gt;
-tc = {'id': 'TC_FILE_002', 'module': 'File Upload', 'name': 'Upload Leaf Image JPG Format', 'priority': 'High', ...}
-    @pytest.mark.parametrize("tc", test_cases, ids=lambda x: x["id"])
-    def test_regression_case(shared_driver, tc):
-        """Executes the specific test case via hybrid or simulated path."""
-        test_id = tc["id"]
-        module = tc["module"]
-        name = tc["name"]
-        is_mock = not hasattr(shared_driver, "find_element")
-        print(f"\n[Running Test] {test_id} - {name} ({module})")
-        # 1. Active Appium Session (Live Hybrid Actions)
-        if not is_mock:
-            try:
-                # Login E2E
-                if test_id == "TC_AUTH_001":
-                    login_page = LoginPage(shared_driver)
-                    login_page.login("testfarmer@example.com", "TestFarmer123!")
-                    time.sleep(4)
-                    home_page = HomePage(shared_driver)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Login verification failed"
-                    home_page.capture_screenshot("TC_AUTH_001_success")
-                # Quick Actions grid scroll/check
-                elif test_id == "TC_DASH_002":
-                    home_page = HomePage(shared_driver)
-                    home_page.swipe(720, 1600, 720, 800, 300)
-                    assert home_page.wait_for_element(home_page.MARKET_TILE) is not None, "Quick Actions grid failed to scroll/load"
-                    home_page.capture_screenshot("TC_DASH_002_success")
-                # Navigate to Crops Screen
-                elif test_id == "TC_NAV_001":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.CROPS_TAB)
-                    crops_title = (By.XPATH, "//*[contains(@content-desc, 'Farm Management')] | //*[contains(@text, 'Farm Management')]")
-                    assert home_page.wait_for_element(crops_title) is not None, "Navigation to Crops failed"
-                    home_page.capture_screenshot("TC_NAV_001_success")
-                # Navigation back to Home
-                elif test_id == "TC_NAV_003":
-                    home_page = HomePage(shared_driver)
-                    home_page.click(home_page.HOME_TAB)
-                    assert home_page.wait_for_element(home_page.CROPS_TAB) is not None, "Navigation back to Home failed"
-                    home_page.capture_screenshot("TC_NAV_003_success")
-                # Simulated actions for others when driver is active
-                else:
-                    # Basic assertion to pass successfully
-                    assert tc["status"] == "passed"
-            except Exception as e:
-                # Save screenshot on failure
-                screenshots_dir = os.path.join(
-                    os.path.dirname(os.path.dirname(os.path.abspath(__file__))),
-                    "Test Results", "Screenshots"
-                )
-                os.makedirs(screenshots_dir, exist_ok=True)
-                screenshot_path = os.path.join(screenshots_dir, f"fail_{test_id}.png")
-                try:
-                    shared_driver.save_screenshot(screenshot_path)
-                except Exception:
-                    pass
-                raise e
-        # 2. Simulated Execution (No live Appium driver - local unit testing or regression scale)
-        else:
-            # Verify correctness of test case data structure
-            assert tc["id"] is not None
-            assert tc["module"] is not None
-            assert tc["name"] is not None
-            assert tc["priority"] in ["Critical", "High", "Medium", "Low"]
-            assert len(tc["steps"]) &gt; 0
-            assert tc["expected"] is not None
-            # Simulate some test cases failing to test reporting and failure criteria if needed
-            # (For regression verification, we will ensure &gt;95% pass rate so the workflow passes)
-            if test_id in ["TC_AUTH_010", "TC_FORM_008", "TC_FILE_002"]:
-                # Intentionally fail these 3 test cases to match the failure examples in summary
-                tc["status"] = "failed"
-                tc["actual_result"] = "Validation elements missing or mismatch"
-&gt;               raise AssertionError(f"Simulated failure for {test_id}: {tc['actual_result']}")
-E               AssertionError: Simulated failure for TC_FILE_002: Validation elements missing or mismatch
-tests/mobile_e2e/test_suites/test_regression_400.py:145: AssertionError</t>
+                payload_dict = json.loads(payload)
+            except (json.JSONDecodeError, TypeError):
+                return
+            if not isinstance(payload_dict, dict):
+                return
+        value = payload_dict.get('value')
+        if not isinstance(value, dict):
+            return
+        error = value.get('error')
+        if not error:
+            return
+        message = value.get('message', error)
+        stacktrace = value.get('stacktrace', '')
+        # In theory, we should also be checking HTTP status codes.
+        # Java client, for example, prints a warning if the actual `error`
+        # value does not match to the response's HTTP status code.
+        exception_class: Type[sel_exceptions.WebDriverException] = ERROR_TO_EXC_MAPPING.get(
+            error, sel_exceptions.WebDriverException
+        )
+        if exception_class is sel_exceptions.WebDriverException and message:
+            if message == 'No such context found.':
+                exception_class = appium_exceptions.NoSuchContextException
+            elif message == 'That command could not be executed in the current context.':
+                exception_class = appium_exceptions.InvalidSwitchToTargetException
+        if exception_class is sel_exceptions.UnexpectedAlertPresentException:
+            raise sel_exceptions.UnexpectedAlertPresentException(
+                msg=message,
+                stacktrace=format_stacktrace(stacktrace),
+                alert_text=value.get('data'),
+            )
+&gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
+E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       Stacktrace:
+E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:366)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:378)
+E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
+E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.findElement(ElementLocationHelpers.java:151)
+E       	at io.appium.uiautomator2.handler.FindElement.safeHandle(FindElement.java:60)
+E       	at io.appium.uiautomator2.handler.request.SafeRequestHandler.handle(SafeRequestHandler.java:59)
+E       	at io.appium.uiautomator2.server.AppiumServlet.handleRequest(AppiumServlet.java:267)
+E       	at io.appium.uiautomator2.server.AppiumServlet.handleHttpRequest(AppiumServlet.java:261)
+E       	at io.appium.uiautomator2.http.ServerHandler.channelRead(ServerHandler.java:77)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
+E       	at io.netty.handler.codec.MessageToMessageDecoder.channelRead(MessageToMessageDecoder.java:107)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
+E       	at io.netty.channel.CombinedChannelDuplexHandler$DelegatingChannelHandlerContext.fireChannelRead(CombinedChannelDuplexHandler.java:434)
+E       	at io.netty.handler.codec.ByteToMessageDecoder.fireChannelRead(ByteToMessageDecoder.java:361)
+E       	at io.netty.handler.codec.ByteToMessageDecoder.channelRead(ByteToMessageDecoder.java:325)
+E       	at io.netty.channel.CombinedChannelDuplexHandler.channelRead(CombinedChannelDuplexHandler.java:249)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
+E       	at io.netty.handler.timeout.IdleStateHandler.channelRead(IdleStateHandler.java:288)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
+E       	at io.netty.channel.DefaultChannelPipeline$HeadContext.channelRead(DefaultChannelPipeline.java:1429)
+E       	at io.netty.channel.DefaultChannelPipeline.fireChannelRead(DefaultChannelPipeline.java:918)
+E       	at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:176)
+E       	at io.netty.channel.nio.AbstractNioChannel$AbstractNioUnsafe.handle(AbstractNioChannel.java:445)
+E       	at io.netty.channel.nio.NioIoHandler$DefaultNioRegistration.handle(NioIoHandler.java:388)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKey(NioIoHandler.java:596)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeysOptimized(NioIoHandler.java:571)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeys(NioIoHandler.java:512)
+E       	at io.netty.channel.nio.NioIoHandler.run(NioIoHandler.java:484)
+E       	at io.netty.channel.SingleThreadIoEventLoop.runIo(SingleThreadIoEventLoop.java:225)
+E       	at io.netty.channel.SingleThreadIoEventLoop.run(SingleThreadIoEventLoop.java:196)
+E       	at io.netty.util.concurrent.SingleThreadEventExecutor$5.run(SingleThreadEventExecutor.java:1195)
+E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
+E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
+E       	at java.lang.Thread.run(Thread.java:919)
+E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.toStream(AccessibilityNodeInfoDumper.java:228)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)
+E       	... 33 more
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/appium/webdriver/errorhandler.py:125: WebDriverException</t>
         </is>
       </c>
     </row>
